--- a/htr-update-fr-medication/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/htr-update-fr-medication/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T08:28:14+00:00</t>
+    <t>2026-09-04T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,7 +560,7 @@
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
     &lt;code value="adr"/&gt;
-    &lt;display value="Advance Directive"/&gt;
+    &lt;display value="Advanced Care Directive"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
